--- a/STA01D.xlsx
+++ b/STA01D.xlsx
@@ -172,457 +172,457 @@
     <t>UHU LEM ALL PURPOS20</t>
   </si>
   <si>
+    <t>20138845</t>
+  </si>
+  <si>
+    <t>LARISST SPR GLUE 10G</t>
+  </si>
+  <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>10000656</t>
+  </si>
+  <si>
+    <t>AICA LEM AIBON 601</t>
+  </si>
+  <si>
     <t>8</t>
   </si>
   <si>
-    <t>20138845</t>
-  </si>
-  <si>
-    <t>LARISST SPR GLUE 10G</t>
-  </si>
-  <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>10000656</t>
-  </si>
-  <si>
-    <t>AICA LEM AIBON 601</t>
+    <t>20130794</t>
+  </si>
+  <si>
+    <t>JYKO ERA 526 B20 PCK</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
-    <t>20130794</t>
-  </si>
-  <si>
-    <t>JYKO ERA 526 B20 PCK</t>
+    <t>20118380</t>
+  </si>
+  <si>
+    <t>JYKO OIL PSTL OP-12S</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
-    <t>20118380</t>
-  </si>
-  <si>
-    <t>JYKO OIL PSTL OP-12S</t>
+    <t>10022100</t>
+  </si>
+  <si>
+    <t>SINDU ORIGAMI 100S B</t>
+  </si>
+  <si>
+    <t>10022101</t>
+  </si>
+  <si>
+    <t>SINDU ORIGAMI 100S T</t>
+  </si>
+  <si>
+    <t>20122345</t>
+  </si>
+  <si>
+    <t>DELI PAPER CLIP 0024</t>
+  </si>
+  <si>
+    <t>20126392</t>
+  </si>
+  <si>
+    <t>PSTIT SS NT FLA 135S</t>
+  </si>
+  <si>
+    <t>20036265</t>
+  </si>
+  <si>
+    <t>JOYKO GLUE STIK GS15</t>
+  </si>
+  <si>
+    <t>20122425</t>
+  </si>
+  <si>
+    <t>JOYKO TWIST CRYN 12S</t>
+  </si>
+  <si>
+    <t>20137691</t>
+  </si>
+  <si>
+    <t>ADINATA PENC.TROP M3</t>
+  </si>
+  <si>
+    <t>20138868</t>
+  </si>
+  <si>
+    <t>RHINO DIY BEAD CHARM</t>
+  </si>
+  <si>
+    <t>20132581</t>
+  </si>
+  <si>
+    <t>STNRY ICE CRM ERASER</t>
+  </si>
+  <si>
+    <t>20136257</t>
+  </si>
+  <si>
+    <t>STNRY SEA ANIMAL PEN</t>
+  </si>
+  <si>
+    <t>20136258</t>
+  </si>
+  <si>
+    <t>STNRY DRAGON PEN</t>
+  </si>
+  <si>
+    <t>20136260</t>
+  </si>
+  <si>
+    <t>STNRY DIY PNCL 2B 3S</t>
+  </si>
+  <si>
+    <t>20136261</t>
+  </si>
+  <si>
+    <t>STNRY DIY BRCK RULER</t>
+  </si>
+  <si>
+    <t>20136262</t>
+  </si>
+  <si>
+    <t>STNRY DIY BRCK SHRPN</t>
+  </si>
+  <si>
+    <t>20139864</t>
+  </si>
+  <si>
+    <t>STNRY HP DUCK ERASER</t>
+  </si>
+  <si>
+    <t>20139865</t>
+  </si>
+  <si>
+    <t>STNRY FST FD GLU STK</t>
+  </si>
+  <si>
+    <t>20139866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STNRY SMR FRUIT PEN </t>
+  </si>
+  <si>
+    <t>20139867</t>
+  </si>
+  <si>
+    <t>STNRY ICE/C PUSH PEN</t>
+  </si>
+  <si>
+    <t>20139868</t>
+  </si>
+  <si>
+    <t>STNRY FAST FOOD PEN</t>
+  </si>
+  <si>
+    <t>20139869</t>
+  </si>
+  <si>
+    <t>STNRY CMERA TOPR PEN</t>
+  </si>
+  <si>
+    <t>20139871</t>
+  </si>
+  <si>
+    <t>STNRY FASTN FD PNCIL</t>
+  </si>
+  <si>
+    <t>20139873</t>
+  </si>
+  <si>
+    <t>STNRY SUMMER RULER</t>
+  </si>
+  <si>
+    <t>20139874</t>
+  </si>
+  <si>
+    <t>STNRY FAST FD SHARPN</t>
+  </si>
+  <si>
+    <t>20139881</t>
+  </si>
+  <si>
+    <t>STNRY LIT.STICK NOTE</t>
+  </si>
+  <si>
+    <t>20105929</t>
+  </si>
+  <si>
+    <t>STNRY VGTBLE 3D PEN</t>
+  </si>
+  <si>
+    <t>20133801</t>
+  </si>
+  <si>
+    <t>ADNTA SCRET PEN MIX2</t>
+  </si>
+  <si>
+    <t>20137049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADNTA PEN W/TOPPER  </t>
+  </si>
+  <si>
+    <t>20137050</t>
+  </si>
+  <si>
+    <t>ADNTA GEL PEN RUBBER</t>
+  </si>
+  <si>
+    <t>20055289</t>
+  </si>
+  <si>
+    <t>A/N STICKER  PUFFY</t>
+  </si>
+  <si>
+    <t>20093329</t>
+  </si>
+  <si>
+    <t>DELI SCISSORS 6021</t>
+  </si>
+  <si>
+    <t>20098010</t>
+  </si>
+  <si>
+    <t>ADNTA NOTE STAT.MIX1</t>
+  </si>
+  <si>
+    <t>20098390</t>
+  </si>
+  <si>
+    <t>DELI GLUE STCK 6366A</t>
+  </si>
+  <si>
+    <t>20098391</t>
+  </si>
+  <si>
+    <t>DELI CRCT PEN H10200</t>
+  </si>
+  <si>
+    <t>20098398</t>
+  </si>
+  <si>
+    <t>DELI PR.MRKR BLU&amp;BLC</t>
+  </si>
+  <si>
+    <t>20098406</t>
+  </si>
+  <si>
+    <t>DELI CTTER 2022/2024</t>
+  </si>
+  <si>
+    <t>20128687</t>
+  </si>
+  <si>
+    <t>ADNTA M/MNI NOTES 3S</t>
+  </si>
+  <si>
+    <t>20132577</t>
+  </si>
+  <si>
+    <t>STNRY ORGMI DUCK PEN</t>
+  </si>
+  <si>
+    <t>20137718</t>
+  </si>
+  <si>
+    <t>STNRY RABBIT ERASER</t>
+  </si>
+  <si>
+    <t>20137719</t>
+  </si>
+  <si>
+    <t>STNRY PEN CUTE TROPR</t>
+  </si>
+  <si>
+    <t>20137720</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STNRY CACTUS GLUE </t>
+  </si>
+  <si>
+    <t>20138869</t>
+  </si>
+  <si>
+    <t>RHINO CHRYSTAL WHIMP</t>
+  </si>
+  <si>
+    <t>20138874</t>
+  </si>
+  <si>
+    <t>RHINO BUBBLE TEA</t>
+  </si>
+  <si>
+    <t>20052056</t>
+  </si>
+  <si>
+    <t>STICKER 12.500 PCS</t>
+  </si>
+  <si>
+    <t>20057932</t>
+  </si>
+  <si>
+    <t>STICKER GIRLS</t>
+  </si>
+  <si>
+    <t>20085048</t>
+  </si>
+  <si>
+    <t>A/N STCKR BOOK 7 SCN</t>
+  </si>
+  <si>
+    <t>20096351</t>
+  </si>
+  <si>
+    <t>ADNTA STCKR ML.PONY</t>
+  </si>
+  <si>
+    <t>20130761</t>
+  </si>
+  <si>
+    <t>ADINATA EMBSD STCKER</t>
+  </si>
+  <si>
+    <t>20130762</t>
+  </si>
+  <si>
+    <t>ADINATA SHKER STCKER</t>
+  </si>
+  <si>
+    <t>20130795</t>
+  </si>
+  <si>
+    <t>RHINO STICKER ASTD</t>
+  </si>
+  <si>
+    <t>20132476</t>
+  </si>
+  <si>
+    <t>DADI SHAKING STICKER</t>
+  </si>
+  <si>
+    <t>20132477</t>
+  </si>
+  <si>
+    <t>DADI DIY STICKER</t>
+  </si>
+  <si>
+    <t>20133141</t>
+  </si>
+  <si>
+    <t>RHINO STICKER PUFFY</t>
+  </si>
+  <si>
+    <t>20135718</t>
+  </si>
+  <si>
+    <t>CPCRN STCKR PCK ASST</t>
+  </si>
+  <si>
+    <t>20136100</t>
+  </si>
+  <si>
+    <t>RHINO STICKER FAMILY</t>
+  </si>
+  <si>
+    <t>20136249</t>
+  </si>
+  <si>
+    <t>DADI DIY STCKR PLYST</t>
+  </si>
+  <si>
+    <t>20136853</t>
+  </si>
+  <si>
+    <t>ADINATA DC/FELT STKR</t>
+  </si>
+  <si>
+    <t>20136854</t>
+  </si>
+  <si>
+    <t>ADINATA JELY STICKER</t>
+  </si>
+  <si>
+    <t>20137074</t>
+  </si>
+  <si>
+    <t>ADINATA FRAME STICKR</t>
+  </si>
+  <si>
+    <t>20137075</t>
+  </si>
+  <si>
+    <t>ADINATA DIY ST STCKR</t>
+  </si>
+  <si>
+    <t>20137098</t>
+  </si>
+  <si>
+    <t>RHINO STICKER KANAMA</t>
+  </si>
+  <si>
+    <t>10022333</t>
+  </si>
+  <si>
+    <t>SNOWMAN SPD KCL 3'S</t>
+  </si>
+  <si>
+    <t>10024555</t>
+  </si>
+  <si>
+    <t>F/C PAKET UMPTN SET</t>
+  </si>
+  <si>
+    <t>20032859</t>
+  </si>
+  <si>
+    <t>DADI PVC PENCASE+</t>
+  </si>
+  <si>
+    <t>20137292</t>
+  </si>
+  <si>
+    <t>IDM GEL PEN 3'S</t>
+  </si>
+  <si>
+    <t>20128379</t>
+  </si>
+  <si>
+    <t>KENKO G.PEN+LGHTR 2S</t>
+  </si>
+  <si>
+    <t>10010596</t>
+  </si>
+  <si>
+    <t>F/C PENCIL WN 114462</t>
+  </si>
+  <si>
+    <t>10011819</t>
+  </si>
+  <si>
+    <t>SNOWMAN SPDL WRN 12S</t>
+  </si>
+  <si>
+    <t>20012674</t>
+  </si>
+  <si>
+    <t>ADINATA STTIONARY 7S</t>
+  </si>
+  <si>
+    <t>20130763</t>
+  </si>
+  <si>
+    <t>KENKO CR.TAPE CT-902</t>
   </si>
   <si>
     <t>11</t>
-  </si>
-  <si>
-    <t>10022100</t>
-  </si>
-  <si>
-    <t>SINDU ORIGAMI 100S B</t>
-  </si>
-  <si>
-    <t>10022101</t>
-  </si>
-  <si>
-    <t>SINDU ORIGAMI 100S T</t>
-  </si>
-  <si>
-    <t>20122345</t>
-  </si>
-  <si>
-    <t>DELI PAPER CLIP 0024</t>
-  </si>
-  <si>
-    <t>20126392</t>
-  </si>
-  <si>
-    <t>PSTIT SS NT FLA 135S</t>
-  </si>
-  <si>
-    <t>20036265</t>
-  </si>
-  <si>
-    <t>JOYKO GLUE STIK GS15</t>
-  </si>
-  <si>
-    <t>20122425</t>
-  </si>
-  <si>
-    <t>JOYKO TWIST CRYN 12S</t>
-  </si>
-  <si>
-    <t>20137691</t>
-  </si>
-  <si>
-    <t>ADINATA PENC.TROP M3</t>
-  </si>
-  <si>
-    <t>20138868</t>
-  </si>
-  <si>
-    <t>RHINO DIY BEAD CHARM</t>
-  </si>
-  <si>
-    <t>20132581</t>
-  </si>
-  <si>
-    <t>STNRY ICE CRM ERASER</t>
-  </si>
-  <si>
-    <t>20136257</t>
-  </si>
-  <si>
-    <t>STNRY SEA ANIMAL PEN</t>
-  </si>
-  <si>
-    <t>20136258</t>
-  </si>
-  <si>
-    <t>STNRY DRAGON PEN</t>
-  </si>
-  <si>
-    <t>20136260</t>
-  </si>
-  <si>
-    <t>STNRY DIY PNCL 2B 3S</t>
-  </si>
-  <si>
-    <t>20136261</t>
-  </si>
-  <si>
-    <t>STNRY DIY BRCK RULER</t>
-  </si>
-  <si>
-    <t>20136262</t>
-  </si>
-  <si>
-    <t>STNRY DIY BRCK SHRPN</t>
-  </si>
-  <si>
-    <t>20139864</t>
-  </si>
-  <si>
-    <t>STNRY HP DUCK ERASER</t>
-  </si>
-  <si>
-    <t>20139865</t>
-  </si>
-  <si>
-    <t>STNRY FST FD GLU STK</t>
-  </si>
-  <si>
-    <t>20139866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STNRY SMR FRUIT PEN </t>
-  </si>
-  <si>
-    <t>20139867</t>
-  </si>
-  <si>
-    <t>STNRY ICE/C PUSH PEN</t>
-  </si>
-  <si>
-    <t>20139868</t>
-  </si>
-  <si>
-    <t>STNRY FAST FOOD PEN</t>
-  </si>
-  <si>
-    <t>20139869</t>
-  </si>
-  <si>
-    <t>STNRY CMERA TOPR PEN</t>
-  </si>
-  <si>
-    <t>20139871</t>
-  </si>
-  <si>
-    <t>STNRY FASTN FD PNCIL</t>
-  </si>
-  <si>
-    <t>20139873</t>
-  </si>
-  <si>
-    <t>STNRY SUMMER RULER</t>
-  </si>
-  <si>
-    <t>20139874</t>
-  </si>
-  <si>
-    <t>STNRY FAST FD SHARPN</t>
-  </si>
-  <si>
-    <t>20139881</t>
-  </si>
-  <si>
-    <t>STNRY LIT.STICK NOTE</t>
-  </si>
-  <si>
-    <t>20105929</t>
-  </si>
-  <si>
-    <t>STNRY VGTBLE 3D PEN</t>
-  </si>
-  <si>
-    <t>20133801</t>
-  </si>
-  <si>
-    <t>ADNTA SCRET PEN MIX2</t>
-  </si>
-  <si>
-    <t>20137049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADNTA PEN W/TOPPER  </t>
-  </si>
-  <si>
-    <t>20137050</t>
-  </si>
-  <si>
-    <t>ADNTA GEL PEN RUBBER</t>
-  </si>
-  <si>
-    <t>20128687</t>
-  </si>
-  <si>
-    <t>ADNTA M/MNI NOTES 3S</t>
-  </si>
-  <si>
-    <t>20137718</t>
-  </si>
-  <si>
-    <t>STNRY RABBIT ERASER</t>
-  </si>
-  <si>
-    <t>20137719</t>
-  </si>
-  <si>
-    <t>STNRY PEN CUTE TROPR</t>
-  </si>
-  <si>
-    <t>20137720</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STNRY CACTUS GLUE </t>
-  </si>
-  <si>
-    <t>20055289</t>
-  </si>
-  <si>
-    <t>A/N STICKER  PUFFY</t>
-  </si>
-  <si>
-    <t>20093329</t>
-  </si>
-  <si>
-    <t>DELI SCISSORS 6021</t>
-  </si>
-  <si>
-    <t>20098010</t>
-  </si>
-  <si>
-    <t>ADNTA NOTE STAT.MIX1</t>
-  </si>
-  <si>
-    <t>20098390</t>
-  </si>
-  <si>
-    <t>DELI GLUE STCK 6366A</t>
-  </si>
-  <si>
-    <t>20098391</t>
-  </si>
-  <si>
-    <t>DELI CRCT PEN H10200</t>
-  </si>
-  <si>
-    <t>20098398</t>
-  </si>
-  <si>
-    <t>DELI PR.MRKR BLU&amp;BLC</t>
-  </si>
-  <si>
-    <t>20098406</t>
-  </si>
-  <si>
-    <t>DELI CTTER 2022/2024</t>
-  </si>
-  <si>
-    <t>20132577</t>
-  </si>
-  <si>
-    <t>STNRY ORGMI DUCK PEN</t>
-  </si>
-  <si>
-    <t>20138869</t>
-  </si>
-  <si>
-    <t>RHINO CHRYSTAL WHIMP</t>
-  </si>
-  <si>
-    <t>20138874</t>
-  </si>
-  <si>
-    <t>RHINO BUBBLE TEA</t>
-  </si>
-  <si>
-    <t>20052056</t>
-  </si>
-  <si>
-    <t>STICKER 12.500 PCS</t>
-  </si>
-  <si>
-    <t>20057932</t>
-  </si>
-  <si>
-    <t>STICKER GIRLS</t>
-  </si>
-  <si>
-    <t>20085048</t>
-  </si>
-  <si>
-    <t>A/N STCKR BOOK 7 SCN</t>
-  </si>
-  <si>
-    <t>20096351</t>
-  </si>
-  <si>
-    <t>ADNTA STCKR ML.PONY</t>
-  </si>
-  <si>
-    <t>20130761</t>
-  </si>
-  <si>
-    <t>ADINATA EMBSD STCKER</t>
-  </si>
-  <si>
-    <t>20130762</t>
-  </si>
-  <si>
-    <t>ADINATA SHKER STCKER</t>
-  </si>
-  <si>
-    <t>20130795</t>
-  </si>
-  <si>
-    <t>RHINO STICKER ASTD</t>
-  </si>
-  <si>
-    <t>20132476</t>
-  </si>
-  <si>
-    <t>DADI SHAKING STICKER</t>
-  </si>
-  <si>
-    <t>20132477</t>
-  </si>
-  <si>
-    <t>DADI DIY STICKER</t>
-  </si>
-  <si>
-    <t>20133141</t>
-  </si>
-  <si>
-    <t>RHINO STICKER PUFFY</t>
-  </si>
-  <si>
-    <t>20135718</t>
-  </si>
-  <si>
-    <t>CPCRN STCKR PCK ASST</t>
-  </si>
-  <si>
-    <t>20136100</t>
-  </si>
-  <si>
-    <t>RHINO STICKER FAMILY</t>
-  </si>
-  <si>
-    <t>20136249</t>
-  </si>
-  <si>
-    <t>DADI DIY STCKR PLYST</t>
-  </si>
-  <si>
-    <t>20136853</t>
-  </si>
-  <si>
-    <t>ADINATA DC/FELT STKR</t>
-  </si>
-  <si>
-    <t>20136854</t>
-  </si>
-  <si>
-    <t>ADINATA JELY STICKER</t>
-  </si>
-  <si>
-    <t>20137074</t>
-  </si>
-  <si>
-    <t>ADINATA FRAME STICKR</t>
-  </si>
-  <si>
-    <t>20137075</t>
-  </si>
-  <si>
-    <t>ADINATA DIY ST STCKR</t>
-  </si>
-  <si>
-    <t>20137098</t>
-  </si>
-  <si>
-    <t>RHINO STICKER KANAMA</t>
-  </si>
-  <si>
-    <t>10022333</t>
-  </si>
-  <si>
-    <t>SNOWMAN SPD KCL 3'S</t>
-  </si>
-  <si>
-    <t>10024555</t>
-  </si>
-  <si>
-    <t>F/C PAKET UMPTN SET</t>
-  </si>
-  <si>
-    <t>20032859</t>
-  </si>
-  <si>
-    <t>DADI PVC PENCASE+</t>
-  </si>
-  <si>
-    <t>20137292</t>
-  </si>
-  <si>
-    <t>IDM GEL PEN 3'S</t>
-  </si>
-  <si>
-    <t>20128379</t>
-  </si>
-  <si>
-    <t>KENKO G.PEN+LGHTR 2S</t>
-  </si>
-  <si>
-    <t>10010596</t>
-  </si>
-  <si>
-    <t>F/C PENCIL WN 114462</t>
-  </si>
-  <si>
-    <t>10011819</t>
-  </si>
-  <si>
-    <t>SNOWMAN SPDL WRN 12S</t>
-  </si>
-  <si>
-    <t>20012674</t>
-  </si>
-  <si>
-    <t>ADINATA STTIONARY 7S</t>
-  </si>
-  <si>
-    <t>20130763</t>
-  </si>
-  <si>
-    <t>KENKO CR.TAPE CT-902</t>
   </si>
   <si>
     <t>20129005</t>
@@ -1533,7 +1533,7 @@
         <v>10</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>21</v>
@@ -1553,7 +1553,7 @@
         <v>10</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>21</v>
@@ -1573,7 +1573,7 @@
         <v>10</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>21</v>
@@ -1593,7 +1593,7 @@
         <v>10</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>21</v>
@@ -1613,7 +1613,7 @@
         <v>10</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>21</v>
@@ -1633,7 +1633,7 @@
         <v>10</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>21</v>
@@ -1653,7 +1653,7 @@
         <v>10</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>21</v>
@@ -1673,7 +1673,7 @@
         <v>10</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>21</v>
@@ -1681,10 +1681,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -1693,18 +1693,18 @@
         <v>10</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1713,7 +1713,7 @@
         <v>10</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>21</v>
@@ -1721,10 +1721,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1733,7 +1733,7 @@
         <v>10</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>21</v>
@@ -1741,10 +1741,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -1753,7 +1753,7 @@
         <v>10</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>21</v>
@@ -1761,10 +1761,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -1781,10 +1781,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
@@ -1801,10 +1801,10 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>70</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>71</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>3</v>
@@ -1821,10 +1821,10 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>72</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>73</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -1841,10 +1841,10 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
@@ -1861,10 +1861,10 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>77</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>3</v>
@@ -1881,10 +1881,10 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>78</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>79</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>3</v>
@@ -1893,7 +1893,7 @@
         <v>17</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>21</v>
@@ -1901,10 +1901,10 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -1913,7 +1913,7 @@
         <v>17</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>21</v>
@@ -1921,10 +1921,10 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>83</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -1941,10 +1941,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -1961,10 +1961,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>87</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -1981,10 +1981,10 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
@@ -2001,10 +2001,10 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>3</v>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>3</v>
@@ -2041,10 +2041,10 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>95</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>3</v>
@@ -2061,10 +2061,10 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>3</v>
@@ -2081,10 +2081,10 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>98</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>99</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>3</v>
@@ -2101,10 +2101,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>101</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>3</v>
@@ -2121,10 +2121,10 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B45" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>103</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>3</v>
@@ -2141,10 +2141,10 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B46" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>105</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>3</v>
@@ -2161,10 +2161,10 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>106</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>107</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>3</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B48" s="1" t="s">
         <v>108</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>109</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>3</v>
@@ -2201,10 +2201,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="B49" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>111</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>3</v>
@@ -2221,10 +2221,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>113</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>3</v>
@@ -2241,10 +2241,10 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B51" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>115</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>3</v>
@@ -2261,10 +2261,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>116</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>117</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>3</v>
@@ -2281,10 +2281,10 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>119</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>3</v>
@@ -2301,10 +2301,10 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>120</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>121</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>3</v>
@@ -2321,11 +2321,11 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="C55" s="1" t="s">
         <v>3</v>
       </c>
@@ -2333,7 +2333,7 @@
         <v>20</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>21</v>
@@ -2341,11 +2341,11 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B56" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B56" s="1" t="s">
-        <v>125</v>
-      </c>
       <c r="C56" s="1" t="s">
         <v>3</v>
       </c>
@@ -2353,19 +2353,19 @@
         <v>20</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B57" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B57" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="C57" s="1" t="s">
         <v>3</v>
       </c>
@@ -2373,19 +2373,19 @@
         <v>20</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B58" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B58" s="1" t="s">
-        <v>129</v>
-      </c>
       <c r="C58" s="1" t="s">
         <v>3</v>
       </c>
@@ -2393,19 +2393,19 @@
         <v>20</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B59" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B59" s="1" t="s">
-        <v>131</v>
-      </c>
       <c r="C59" s="1" t="s">
         <v>3</v>
       </c>
@@ -2413,7 +2413,7 @@
         <v>20</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>21</v>
@@ -2421,11 +2421,11 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B60" s="1" t="s">
-        <v>133</v>
-      </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
       </c>
@@ -2433,7 +2433,7 @@
         <v>20</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>21</v>
@@ -2441,11 +2441,11 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B61" s="1" t="s">
-        <v>135</v>
-      </c>
       <c r="C61" s="1" t="s">
         <v>3</v>
       </c>
@@ -2453,7 +2453,7 @@
         <v>20</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>21</v>
@@ -2461,11 +2461,11 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B62" s="1" t="s">
-        <v>137</v>
-      </c>
       <c r="C62" s="1" t="s">
         <v>3</v>
       </c>
@@ -2473,7 +2473,7 @@
         <v>20</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>21</v>
@@ -2481,11 +2481,11 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>139</v>
-      </c>
       <c r="C63" s="1" t="s">
         <v>3</v>
       </c>
@@ -2493,19 +2493,19 @@
         <v>20</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B64" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B64" s="1" t="s">
-        <v>141</v>
-      </c>
       <c r="C64" s="1" t="s">
         <v>3</v>
       </c>
@@ -2513,19 +2513,19 @@
         <v>20</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B65" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B65" s="1" t="s">
-        <v>143</v>
-      </c>
       <c r="C65" s="1" t="s">
         <v>3</v>
       </c>
@@ -2533,19 +2533,19 @@
         <v>20</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B66" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B66" s="1" t="s">
-        <v>145</v>
-      </c>
       <c r="C66" s="1" t="s">
         <v>3</v>
       </c>
@@ -2553,7 +2553,7 @@
         <v>20</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>5</v>
@@ -2561,11 +2561,11 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>147</v>
-      </c>
       <c r="C67" s="1" t="s">
         <v>3</v>
       </c>
@@ -2573,7 +2573,7 @@
         <v>20</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>21</v>
@@ -2581,11 +2581,11 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>149</v>
-      </c>
       <c r="C68" s="1" t="s">
         <v>3</v>
       </c>
@@ -2593,7 +2593,7 @@
         <v>20</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>21</v>
@@ -2601,11 +2601,11 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B69" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
       </c>
@@ -2613,7 +2613,7 @@
         <v>20</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>21</v>
@@ -2621,11 +2621,11 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B70" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>153</v>
-      </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
       </c>
@@ -2633,7 +2633,7 @@
         <v>20</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>21</v>
@@ -2641,11 +2641,11 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B71" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B71" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="C71" s="1" t="s">
         <v>3</v>
       </c>
@@ -2653,7 +2653,7 @@
         <v>20</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>21</v>
@@ -2661,11 +2661,11 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B72" s="1" t="s">
-        <v>157</v>
-      </c>
       <c r="C72" s="1" t="s">
         <v>3</v>
       </c>
@@ -2673,7 +2673,7 @@
         <v>20</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>21</v>
@@ -2681,11 +2681,11 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B73" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>159</v>
-      </c>
       <c r="C73" s="1" t="s">
         <v>3</v>
       </c>
@@ -2693,7 +2693,7 @@
         <v>20</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>21</v>
@@ -2701,11 +2701,11 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>161</v>
-      </c>
       <c r="C74" s="1" t="s">
         <v>3</v>
       </c>
@@ -2713,7 +2713,7 @@
         <v>20</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>21</v>
@@ -2721,11 +2721,11 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B75" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B75" s="1" t="s">
-        <v>163</v>
-      </c>
       <c r="C75" s="1" t="s">
         <v>3</v>
       </c>
@@ -2733,7 +2733,7 @@
         <v>20</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>21</v>
@@ -2741,11 +2741,11 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B76" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B76" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="C76" s="1" t="s">
         <v>3</v>
       </c>
@@ -2753,7 +2753,7 @@
         <v>20</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>21</v>
@@ -2761,11 +2761,11 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B77" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B77" s="1" t="s">
-        <v>167</v>
-      </c>
       <c r="C77" s="1" t="s">
         <v>3</v>
       </c>
@@ -2773,7 +2773,7 @@
         <v>20</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>21</v>
@@ -2781,11 +2781,11 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B78" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B78" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="C78" s="1" t="s">
         <v>3</v>
       </c>
@@ -2793,7 +2793,7 @@
         <v>20</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>21</v>
@@ -2801,11 +2801,11 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B79" s="1" t="s">
-        <v>171</v>
-      </c>
       <c r="C79" s="1" t="s">
         <v>3</v>
       </c>
@@ -2813,7 +2813,7 @@
         <v>20</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>21</v>
@@ -2821,11 +2821,11 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B80" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="C80" s="1" t="s">
         <v>3</v>
       </c>
@@ -2833,7 +2833,7 @@
         <v>20</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>21</v>
@@ -2841,11 +2841,11 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B81" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B81" s="1" t="s">
-        <v>175</v>
-      </c>
       <c r="C81" s="1" t="s">
         <v>3</v>
       </c>
@@ -2853,7 +2853,7 @@
         <v>20</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="F81" s="1" t="s">
         <v>21</v>
@@ -2861,11 +2861,11 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B82" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B82" s="1" t="s">
-        <v>177</v>
-      </c>
       <c r="C82" s="1" t="s">
         <v>3</v>
       </c>
@@ -2873,7 +2873,7 @@
         <v>20</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="F82" s="1" t="s">
         <v>5</v>
@@ -2881,11 +2881,11 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B83" s="1" t="s">
-        <v>179</v>
-      </c>
       <c r="C83" s="1" t="s">
         <v>3</v>
       </c>
@@ -2893,7 +2893,7 @@
         <v>20</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -2901,11 +2901,11 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B84" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B84" s="1" t="s">
-        <v>181</v>
-      </c>
       <c r="C84" s="1" t="s">
         <v>3</v>
       </c>
@@ -2913,7 +2913,7 @@
         <v>20</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>21</v>
@@ -2921,11 +2921,11 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B85" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B85" s="1" t="s">
-        <v>183</v>
-      </c>
       <c r="C85" s="1" t="s">
         <v>3</v>
       </c>
@@ -2933,7 +2933,7 @@
         <v>20</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>21</v>
@@ -2941,11 +2941,11 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B86" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B86" s="1" t="s">
-        <v>185</v>
-      </c>
       <c r="C86" s="1" t="s">
         <v>3</v>
       </c>
@@ -2953,7 +2953,7 @@
         <v>20</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>21</v>
@@ -2961,10 +2961,10 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="B87" s="1" t="s">
         <v>186</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>187</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>3</v>
@@ -2981,10 +2981,10 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B88" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>189</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>3</v>
@@ -3001,10 +3001,10 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>190</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>191</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>3</v>
@@ -3021,10 +3021,10 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="B90" s="1" t="s">
         <v>192</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>193</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>3</v>
@@ -3041,10 +3041,10 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>194</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>195</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>3</v>
@@ -3061,10 +3061,10 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>196</v>
-      </c>
-      <c r="B92" s="1" t="s">
-        <v>197</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>3</v>
@@ -3073,7 +3073,7 @@
         <v>24</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>21</v>
@@ -3081,10 +3081,10 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B93" s="1" t="s">
         <v>198</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>199</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>3</v>
@@ -3093,7 +3093,7 @@
         <v>24</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>21</v>
@@ -3101,10 +3101,10 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B94" s="1" t="s">
         <v>200</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>201</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>3</v>
@@ -3113,7 +3113,7 @@
         <v>24</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>21</v>
@@ -3121,10 +3121,10 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B95" s="1" t="s">
         <v>202</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>203</v>
       </c>
       <c r="C95" s="1" t="s">
         <v>3</v>
@@ -3133,7 +3133,7 @@
         <v>24</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>65</v>
+        <v>203</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>21</v>
@@ -3353,7 +3353,7 @@
         <v>29</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>21</v>
@@ -3373,7 +3373,7 @@
         <v>29</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>21</v>
@@ -3393,7 +3393,7 @@
         <v>29</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>21</v>
@@ -3413,7 +3413,7 @@
         <v>29</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>65</v>
+        <v>203</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>5</v>
